--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487959_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487959_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.772500000000001</v>
+        <v>7.7506</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5209</v>
+        <v>5.8078</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2516</v>
+        <v>1.9428</v>
       </c>
       <c r="G2" t="n">
         <v>7.646</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3158</v>
+        <v>1.2939</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4244</v>
+        <v>0.7114</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8914</v>
+        <v>0.5825</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5059</v>
+        <v>4.881</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9473</v>
+        <v>4.7435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5586</v>
+        <v>0.1374</v>
       </c>
       <c r="G3" t="n">
         <v>3.3663</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>1.6242</v>
+        <v>0.9993</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8077</v>
+        <v>0.604</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8165</v>
+        <v>0.3953</v>
       </c>
       <c r="V3" t="n">
         <v>-0.674</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.379</v>
+        <v>3.9935</v>
       </c>
       <c r="E4" t="n">
-        <v>2.406</v>
+        <v>2.7116</v>
       </c>
       <c r="F4" t="n">
-        <v>0.973</v>
+        <v>1.2819</v>
       </c>
       <c r="G4" t="n">
         <v>0.0364</v>
@@ -766,13 +766,13 @@
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3888</v>
+        <v>0.2257</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0038</v>
+        <v>0.3094</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3926</v>
+        <v>-0.0837</v>
       </c>
       <c r="V4" t="n">
         <v>2.3438</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>M. GAMEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.02</v>
+        <v>2.1164</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6597</v>
+        <v>3.2244</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6797</v>
+        <v>-1.108</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9562</v>
+        <v>2.6145</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0237</v>
+        <v>1.2062</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0674</v>
+        <v>1.4083</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5217</v>
+        <v>4.064</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8721</v>
+        <v>2.4011</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3505</v>
+        <v>1.6628</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4346</v>
+        <v>-1.4495</v>
       </c>
       <c r="N5" t="n">
+        <v>-1.195</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.2545</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.3964</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5947</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.5019</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.1515</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.2831</v>
-      </c>
-      <c r="P5" t="n">
-        <v>-4.3609</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-6.9378</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.5769</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6844</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.3532</v>
-      </c>
       <c r="U5" t="n">
-        <v>0.3313</v>
+        <v>0.3504</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7403</v>
+        <v>-0.6036</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4033</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.337</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. GAMEZ SANCHEZ</t>
+          <t>D. SHERIFF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3472</v>
+        <v>1.4496</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5113</v>
+        <v>2.3277</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1641</v>
+        <v>-0.8782</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6145</v>
+        <v>0.921</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2062</v>
+        <v>0.5231</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4083</v>
+        <v>0.3979</v>
       </c>
       <c r="J6" t="n">
-        <v>4.064</v>
+        <v>1.439</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4011</v>
+        <v>1.3185</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6628</v>
+        <v>0.1205</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4495</v>
+        <v>-0.518</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.195</v>
+        <v>-0.7953</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2545</v>
+        <v>0.2774</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2673</v>
+        <v>0.5286</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5616</v>
+        <v>0.6728</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2943</v>
+        <v>-0.1442</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SHERIFF</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0535</v>
+        <v>0.4294</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9597</v>
+        <v>-2.8197</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9062</v>
+        <v>3.2492</v>
       </c>
       <c r="G7" t="n">
-        <v>0.921</v>
+        <v>1.9562</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5231</v>
+        <v>3.0237</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3979</v>
+        <v>-1.0674</v>
       </c>
       <c r="J7" t="n">
-        <v>1.439</v>
+        <v>1.5217</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3185</v>
+        <v>2.8721</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1205</v>
+        <v>-1.3505</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.518</v>
+        <v>0.4346</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7953</v>
+        <v>0.1515</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2774</v>
+        <v>0.2831</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-4.3609</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>-6.9378</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9911</v>
+        <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1325</v>
+        <v>1.0938</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3047</v>
+        <v>1.1931</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1723</v>
+        <v>-0.0993</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>1.4033</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2071</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>A. MARTIN BONNEMAISON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7271</v>
+        <v>-0.9368</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7397</v>
+        <v>-1.0535</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4668</v>
+        <v>0.1167</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8749</v>
+        <v>0.3415</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07140000000000001</v>
+        <v>0.2057</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8036</v>
+        <v>0.1358</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0605</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0605</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9355</v>
+        <v>0.3415</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1319</v>
+        <v>0.2057</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8036</v>
+        <v>0.1358</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7929</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7929</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.2873</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6791</v>
+        <v>-0.0624</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1171</v>
+        <v>-0.2249</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9503</v>
+        <v>-1.074</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1424</v>
+        <v>0.1029</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0927</v>
+        <v>-1.1769</v>
       </c>
       <c r="G9" t="n">
         <v>-0.4116</v>
@@ -1156,13 +1156,13 @@
         <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3403</v>
+        <v>0.2166</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4919</v>
+        <v>0.4525</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1516</v>
+        <v>-0.2359</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4737</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARTIN BONNEMAISON</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9649</v>
+        <v>-1.1065</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0535</v>
+        <v>0.3322</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0886</v>
+        <v>-1.4387</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3415</v>
+        <v>-0.8749</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2057</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1358</v>
+        <v>-0.8036</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0605</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3415</v>
+        <v>-0.9355</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2057</v>
+        <v>-0.1319</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1358</v>
+        <v>-0.8036</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9911</v>
+        <v>0.7929</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.7929</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3153</v>
+        <v>0.1826</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0624</v>
+        <v>0.2717</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2529</v>
+        <v>-0.089</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3712</v>
+        <v>-1.8866</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9304</v>
+        <v>-1.7267</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4407</v>
+        <v>-0.16</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4475</v>
@@ -1312,13 +1312,13 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0624</v>
+        <v>0.4221</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2534</v>
+        <v>0.4571</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3158</v>
+        <v>-0.035</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2666</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9484</v>
+        <v>-4.5138</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2773</v>
+        <v>-2.0112</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.6711</v>
+        <v>-2.5026</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6554</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0859</v>
+        <v>0.3487</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3047</v>
+        <v>0.5709</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3907</v>
+        <v>-0.2222</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4142</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.1162</v>
+        <v>11.1028</v>
       </c>
       <c r="E13" t="n">
-        <v>12.3064</v>
+        <v>11.639</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1900999999999993</v>
+        <v>-0.5364000000000002</v>
       </c>
       <c r="G13" t="n">
         <v>12.4925</v>
@@ -1447,7 +1447,7 @@
         <v>16.1714</v>
       </c>
       <c r="L13" t="n">
-        <v>1.6887</v>
+        <v>1.688700000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-5.367800000000001</v>
@@ -1468,16 +1468,16 @@
         <v>13.4793</v>
       </c>
       <c r="S13" t="n">
-        <v>6.5395</v>
+        <v>5.525900000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>5.998900000000001</v>
+        <v>5.331999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5404999999999998</v>
+        <v>0.194</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.555100000000001</v>
+        <v>-2.5551</v>
       </c>
       <c r="W13" t="n">
         <v>6.287100000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>A. BUALÓ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4641</v>
+        <v>2.116</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5988</v>
+        <v>2.116</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1347</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.8348</v>
+        <v>2.116</v>
       </c>
       <c r="H14" t="n">
-        <v>0.187</v>
+        <v>1.5133</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0218</v>
+        <v>0.6027</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1519</v>
+        <v>2.116</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9912</v>
+        <v>1.5133</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1607</v>
+        <v>0.6027</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.9867</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8042</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1825</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3787</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8252</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0853</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2601</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>2.0772</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.3438</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BUALÓ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.116</v>
+        <v>1.8473</v>
       </c>
       <c r="E15" t="n">
-        <v>2.116</v>
+        <v>3.0708</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>-1.2235</v>
       </c>
       <c r="G15" t="n">
-        <v>2.116</v>
+        <v>-0.8348</v>
       </c>
       <c r="H15" t="n">
-        <v>1.5133</v>
+        <v>0.187</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6027</v>
+        <v>-1.0218</v>
       </c>
       <c r="J15" t="n">
-        <v>2.116</v>
+        <v>2.1519</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5133</v>
+        <v>1.9912</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6027</v>
+        <v>0.1607</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-2.9867</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-1.8042</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-1.1825</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.2084</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>0.5573</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0.3489</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.0772</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.3438</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GARCIA GUERRERO</t>
+          <t>A. BUALO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8707</v>
+        <v>0.8067</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5525</v>
+        <v>2.9618</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3183</v>
+        <v>-2.1551</v>
       </c>
       <c r="G16" t="n">
-        <v>0.14</v>
+        <v>-1.2755</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.409</v>
+        <v>-3.3149</v>
       </c>
       <c r="I16" t="n">
-        <v>0.549</v>
+        <v>2.0395</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0605</v>
+        <v>1.9034</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0605</v>
+        <v>-1.0412</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.9446</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0795</v>
+        <v>-3.1789</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4695</v>
+        <v>-2.2737</v>
       </c>
       <c r="O16" t="n">
-        <v>0.549</v>
+        <v>-0.9052</v>
       </c>
       <c r="P16" t="n">
         <v>0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3964</v>
+        <v>2.3787</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2669</v>
+        <v>-1.3995</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4919</v>
+        <v>-0.5807</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2251</v>
+        <v>-0.8187</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0674</v>
+        <v>3.0852</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.6213</v>
       </c>
       <c r="X16" t="n">
-        <v>0.0674</v>
+        <v>-0.5362</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GUTIERREZ</t>
+          <t>A. GARCIA GUERRERO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0216</v>
+        <v>0.5828</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4708</v>
+        <v>0.3487</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4923</v>
+        <v>0.234</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8404</v>
+        <v>0.14</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.005</v>
+        <v>-0.409</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1646</v>
+        <v>0.549</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2908</v>
+        <v>0.0605</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4036</v>
+        <v>0.0605</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.1128</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.1312</v>
+        <v>0.0795</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4085</v>
+        <v>-0.4695</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2774</v>
+        <v>0.549</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1893</v>
+        <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1714</v>
+        <v>-0.0211</v>
       </c>
       <c r="T17" t="n">
-        <v>0.18</v>
+        <v>0.2882</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3513</v>
+        <v>-0.3093</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1992</v>
+        <v>0.0674</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1992</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. BUALO</t>
+          <t>S. MARTINEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3583</v>
+        <v>-0.2429</v>
       </c>
       <c r="E18" t="n">
-        <v>2.045</v>
+        <v>0.1651</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4033</v>
+        <v>-0.4081</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2755</v>
+        <v>-0.8404</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3149</v>
+        <v>-1.005</v>
       </c>
       <c r="I18" t="n">
-        <v>2.0395</v>
+        <v>0.1646</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9034</v>
+        <v>0.2908</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0412</v>
+        <v>0.4036</v>
       </c>
       <c r="L18" t="n">
-        <v>2.9446</v>
+        <v>-0.1128</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1789</v>
+        <v>-1.1312</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2737</v>
+        <v>-1.4085</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9052</v>
+        <v>0.2774</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3787</v>
+        <v>1.1893</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.5644</v>
+        <v>-0.3927</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4975</v>
+        <v>-0.1257</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0669</v>
+        <v>-0.2671</v>
       </c>
       <c r="V18" t="n">
-        <v>3.0852</v>
+        <v>-0.1992</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6213</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5362</v>
+        <v>-0.1992</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. FERNANDEZ CAMPOS</t>
+          <t>D. GARZON ALVAREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.9155</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4531</v>
+        <v>0.1177</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1945</v>
+        <v>-1.0332</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.758</v>
+        <v>-1.8531</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0955</v>
+        <v>-1.0571</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6626</v>
+        <v>-0.796</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3029</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5808</v>
+        <v>1.3525</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2779</v>
+        <v>-0.5586</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0609</v>
+        <v>-2.647</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6762</v>
+        <v>-2.4095</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3847</v>
+        <v>-0.2374</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.784</v>
+        <v>2.5769</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5673</v>
+        <v>-1.0526</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2262</v>
+        <v>-0.2182</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.659</v>
+        <v>-0.8343</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.4044</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7413999999999999</v>
+        <v>-0.1288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. GARZON ALVAREZ</t>
+          <t>H. FERNANDEZ CAMPOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7634</v>
+        <v>-1.4241</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3214</v>
+        <v>-1.37</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0848</v>
+        <v>-0.0541</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8531</v>
+        <v>-1.758</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0571</v>
+        <v>-0.0955</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.796</v>
+        <v>-1.6626</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.3029</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3525</v>
+        <v>1.5808</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5586</v>
+        <v>-1.2779</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.647</v>
+        <v>-2.0609</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.4095</v>
+        <v>-1.6762</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2374</v>
+        <v>-0.3847</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5858</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5769</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9004</v>
+        <v>-0.2092</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0145</v>
+        <v>0.3094</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8859</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4044</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1288</v>
+        <v>0.7413999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.6545</v>
+        <v>-3.7598</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5704</v>
+        <v>-2.7555</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.084</v>
+        <v>-1.0044</v>
       </c>
       <c r="G21" t="n">
         <v>-3.6071</v>
@@ -2092,13 +2092,13 @@
         <v>3.3698</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5388</v>
+        <v>-0.6441</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0056</v>
+        <v>-0.1906</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5332</v>
+        <v>-0.4535</v>
       </c>
       <c r="V21" t="n">
         <v>2.0772</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5653</v>
+        <v>-5.7856</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7857</v>
+        <v>-4.1745</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7795</v>
+        <v>-1.6111</v>
       </c>
       <c r="G22" t="n">
         <v>-1.0294</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3376</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5616</v>
+        <v>0.0496</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7761</v>
+        <v>-0.6076</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4142</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4451</v>
+        <v>-6.5505</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.088</v>
+        <v>-2.2731</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3571</v>
+        <v>-4.2774</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1857</v>
@@ -2248,13 +2248,13 @@
         <v>2.5769</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5608</v>
+        <v>-0.6662</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.756</v>
+        <v>0.0589</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8048</v>
+        <v>-0.7252</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2843</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.0051</v>
+        <v>-13.3256</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7927</v>
+        <v>-1.793000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.2119</v>
+        <v>-11.5329</v>
       </c>
       <c r="G24" t="n">
         <v>-13.128</v>
@@ -2296,7 +2296,7 @@
         <v>-11.1763</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9518</v>
+        <v>-1.951800000000001</v>
       </c>
       <c r="J24" t="n">
         <v>5.0747</v>
@@ -2305,7 +2305,7 @@
         <v>5.2173</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1426000000000001</v>
+        <v>-0.1425999999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-18.2027</v>
@@ -2326,19 +2326,19 @@
         <v>17.84</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.414</v>
+        <v>-4.734999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1482</v>
+        <v>0.1482000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.5624</v>
+        <v>-4.8832</v>
       </c>
       <c r="V24" t="n">
-        <v>2.555099999999999</v>
+        <v>2.5551</v>
       </c>
       <c r="W24" t="n">
-        <v>8.842000000000001</v>
+        <v>8.841999999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-6.287100000000001</v>
